--- a/src/ExcelsiorAspose.Tests/IncludeTests.MultipleSpreadsheetsSameModel_Public.verified.xlsx
+++ b/src/ExcelsiorAspose.Tests/IncludeTests.MultipleSpreadsheetsSameModel_Public.verified.xlsx
@@ -472,17 +472,17 @@
     <col min="1" max="1" width="9.71428571428571" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="14" customHeight="1">
+    <row r="1" spans="1:1" ht="16" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:1" ht="14" customHeight="1">
+    <row r="2" spans="1:1" ht="16" customHeight="1">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:1" ht="14" customHeight="1">
+    <row r="3" spans="1:1" ht="16" customHeight="1">
       <c r="A3" s="2" t="s">
         <v>2</v>
       </c>

--- a/src/ExcelsiorAspose.Tests/IncludeTests.MultipleSpreadsheetsSameModel_Public.verified.xlsx
+++ b/src/ExcelsiorAspose.Tests/IncludeTests.MultipleSpreadsheetsSameModel_Public.verified.xlsx
@@ -472,17 +472,17 @@
     <col min="1" max="1" width="9.71428571428571" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="16" customHeight="1">
+    <row r="1" spans="1:1" ht="14" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:1" ht="16" customHeight="1">
+    <row r="2" spans="1:1" ht="14" customHeight="1">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:1" ht="16" customHeight="1">
+    <row r="3" spans="1:1" ht="14" customHeight="1">
       <c r="A3" s="2" t="s">
         <v>2</v>
       </c>
